--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Business Cycle Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Business Cycle Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="243">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Business Cycle Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -106,6 +106,12 @@
     <t>Automobiles</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
     <t>Ultratech Cement Ltd.</t>
   </si>
   <si>
@@ -124,12 +130,6 @@
     <t>Telecom - Services</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Cummins India Ltd.</t>
   </si>
   <si>
@@ -154,6 +154,15 @@
     <t>Power</t>
   </si>
   <si>
+    <t>DLF Ltd.</t>
+  </si>
+  <si>
+    <t>INE271C01023</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
   </si>
   <si>
@@ -163,6 +172,21 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
+  </si>
+  <si>
     <t>Interglobe Aviation Ltd.</t>
   </si>
   <si>
@@ -172,13 +196,13 @@
     <t>Transport Services</t>
   </si>
   <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
   </si>
   <si>
     <t>ICICI Prudential Life Insurance Company Ltd.</t>
@@ -187,13 +211,316 @@
     <t>INE726G01019</t>
   </si>
   <si>
-    <t>DLF Ltd.</t>
-  </si>
-  <si>
-    <t>INE271C01023</t>
-  </si>
-  <si>
-    <t>Realty</t>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>NHPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE848E01016</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
+  </si>
+  <si>
+    <t>Shree Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE070A01015</t>
+  </si>
+  <si>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>Affle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE00WC01027</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Siemens Ltd.</t>
+  </si>
+  <si>
+    <t>INE003A01024</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Indian Energy Exchange Ltd.</t>
+  </si>
+  <si>
+    <t>INE022Q01020</t>
+  </si>
+  <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>Union Bank Of India</t>
+  </si>
+  <si>
+    <t>INE692A01016</t>
+  </si>
+  <si>
+    <t>Gujarat Pipavav Port Ltd.</t>
+  </si>
+  <si>
+    <t>INE517F01014</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Power Grid Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE752E01010</t>
+  </si>
+  <si>
+    <t>Ingersoll - Rand (India) Ltd</t>
+  </si>
+  <si>
+    <t>INE177A01018</t>
+  </si>
+  <si>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
+    <t>SKF India Ltd.</t>
+  </si>
+  <si>
+    <t>INE640A01023</t>
+  </si>
+  <si>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
+  </si>
+  <si>
+    <t>Gujarat Narmada Valley Fertilizers and Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE113A01013</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Birla Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE340A01012</t>
+  </si>
+  <si>
+    <t>Aarti Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE769A01020</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>ABB India Ltd.</t>
+  </si>
+  <si>
+    <t>INE117A01022</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Timken India Ltd.</t>
+  </si>
+  <si>
+    <t>INE325A01013</t>
+  </si>
+  <si>
+    <t>Graphite India Ltd.</t>
+  </si>
+  <si>
+    <t>INE371A01025</t>
+  </si>
+  <si>
+    <t>Schaeffler India Ltd.</t>
+  </si>
+  <si>
+    <t>INE513A01022</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>TVS Holdings Ltd.</t>
+  </si>
+  <si>
+    <t>INE105A01035</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>JK Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE823G01014</t>
+  </si>
+  <si>
+    <t>Atul Ltd.</t>
+  </si>
+  <si>
+    <t>INE100A01010</t>
+  </si>
+  <si>
+    <t>Navin Fluorine International Ltd.</t>
+  </si>
+  <si>
+    <t>INE048G01026</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Balkrishna Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE787D01026</t>
+  </si>
+  <si>
+    <t>Gujarat State Petronet Ltd.</t>
+  </si>
+  <si>
+    <t>INE246F01010</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Piramal Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE0DK501011</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Indiamart Intermesh Ltd.</t>
+  </si>
+  <si>
+    <t>INE933S01016</t>
+  </si>
+  <si>
+    <t>Retailing</t>
   </si>
   <si>
     <t>Kotak Mahindra Bank Ltd.</t>
@@ -202,304 +529,43 @@
     <t>INE237A01028</t>
   </si>
   <si>
-    <t>Lupin Ltd.</t>
-  </si>
-  <si>
-    <t>INE326A01037</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>HDFC Asset Management Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE127D01025</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>NHPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE848E01016</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
-  </si>
-  <si>
-    <t>Power Grid Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE752E01010</t>
-  </si>
-  <si>
-    <t>Navin Fluorine International Ltd.</t>
-  </si>
-  <si>
-    <t>INE048G01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Gujarat Pipavav Port Ltd.</t>
-  </si>
-  <si>
-    <t>INE517F01014</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Indian Energy Exchange Ltd.</t>
-  </si>
-  <si>
-    <t>INE022Q01020</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Affle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE00WC01027</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
-  </si>
-  <si>
-    <t>Gujarat Narmada Valley Fertilizers and Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE113A01013</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>Aarti Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE769A01020</t>
-  </si>
-  <si>
-    <t>Birla Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE340A01012</t>
-  </si>
-  <si>
-    <t>ICICI Securities Ltd.</t>
-  </si>
-  <si>
-    <t>INE763G01038</t>
-  </si>
-  <si>
-    <t>Timken India Ltd.</t>
-  </si>
-  <si>
-    <t>INE325A01013</t>
-  </si>
-  <si>
-    <t>Hyundai Motor India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0V6F01027</t>
-  </si>
-  <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>Graphite India Ltd.</t>
-  </si>
-  <si>
-    <t>INE371A01025</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Schaeffler India Ltd.</t>
-  </si>
-  <si>
-    <t>INE513A01022</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Atul Ltd.</t>
-  </si>
-  <si>
-    <t>INE100A01010</t>
-  </si>
-  <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>TVS Holdings Ltd.</t>
-  </si>
-  <si>
-    <t>INE105A01035</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Gujarat State Petronet Ltd.</t>
-  </si>
-  <si>
-    <t>INE246F01010</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Ingersoll - Rand (India) Ltd</t>
-  </si>
-  <si>
-    <t>INE177A01018</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Prestige Estates Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE811K01011</t>
-  </si>
-  <si>
-    <t>JK Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE823G01014</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Indiamart Intermesh Ltd.</t>
-  </si>
-  <si>
-    <t>INE933S01016</t>
+    <t>Heidleberg Cement India Ltd.</t>
+  </si>
+  <si>
+    <t>INE578A01017</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
+    <t>Life Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE0J1Y01017</t>
+  </si>
+  <si>
+    <t>Tata Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE092A01019</t>
+  </si>
+  <si>
+    <t>3M India Ltd.</t>
+  </si>
+  <si>
+    <t>INE470A01017</t>
+  </si>
+  <si>
+    <t>Diversified</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
   </si>
   <si>
     <t>The Phoenix Mills Ltd.</t>
@@ -508,79 +574,16 @@
     <t>INE211B01039</t>
   </si>
   <si>
-    <t>Heidleberg Cement India Ltd.</t>
-  </si>
-  <si>
-    <t>INE578A01017</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
-    <t>Nippon Life India Asset Management Ltd</t>
-  </si>
-  <si>
-    <t>INE298J01013</t>
-  </si>
-  <si>
-    <t>Life Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE0J1Y01017</t>
-  </si>
-  <si>
-    <t>Hindustan Aeronautics Ltd.</t>
-  </si>
-  <si>
-    <t>INE066F01020</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>3M India Ltd.</t>
-  </si>
-  <si>
-    <t>INE470A01017</t>
-  </si>
-  <si>
-    <t>Diversified</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Jm Financial Ltd.</t>
-  </si>
-  <si>
-    <t>INE780C01023</t>
-  </si>
-  <si>
-    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE213A01029</t>
-  </si>
-  <si>
-    <t>Oil</t>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Swiggy Ltd</t>
+  </si>
+  <si>
+    <t>INE00H001014</t>
   </si>
   <si>
     <t>Sagar Cements Ltd.</t>
@@ -589,18 +592,6 @@
     <t>INE229C01021</t>
   </si>
   <si>
-    <t>Star Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE460H01021</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
     <t>Foreign Securities/Overseas ETFs</t>
   </si>
   <si>
@@ -646,10 +637,10 @@
     <t>Treasury Bills</t>
   </si>
   <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y191</t>
+    <t>364 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Z115</t>
   </si>
   <si>
     <t>SOV</t>
@@ -658,25 +649,13 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X383</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
-    <t>IN002024Z040</t>
+    <t>IN002025X018</t>
+  </si>
+  <si>
+    <t>IN002024Z198</t>
+  </si>
+  <si>
+    <t>IN002025X042</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -712,21 +691,24 @@
     <t>Index Futures</t>
   </si>
   <si>
-    <t>Ambuja Cements Ltd. $$</t>
+    <t>Axis Bank Ltd. $$</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank Ltd. $$</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd. $$</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd. $$</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd. $$</t>
   </si>
   <si>
     <t>Reliance Industries Ltd. $$</t>
   </si>
   <si>
-    <t>Lupin Ltd. $$</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd. $$</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd. $$</t>
-  </si>
-  <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
   </si>
   <si>
@@ -748,7 +730,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1152,13 +1134,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>165</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>175</xdr:row>
+      <xdr:row>172</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1176,7 +1158,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="31889700"/>
+          <a:off x="666750" y="31318200"/>
           <a:ext cx="3705225" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1191,13 +1173,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>180</xdr:row>
+      <xdr:row>177</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>190</xdr:row>
+      <xdr:row>187</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1215,7 +1197,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="34747200"/>
+          <a:off x="666750" y="34175700"/>
           <a:ext cx="3705225" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1549,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J179"/>
+  <dimension ref="B1:J176"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1649,10 +1631,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1072144.3800000004</v>
+        <v>1224684.47</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9229389787856999</v>
+        <v>0.9440916033404997</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1686,10 +1668,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1072144.3800000004</v>
+        <v>1224684.47</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9229389787856999</v>
+        <v>0.9440916033404997</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1723,10 +1705,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>1036159.2700000003</v>
+        <v>1188718.75</v>
       </c>
       <c r="H9" s="10">
-        <v>0.8919617510031999</v>
+        <v>0.9163661482604997</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1749,13 +1731,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="14">
-        <v>6086591</v>
+        <v>6120866</v>
       </c>
       <c r="G10" s="15">
-        <v>103395.96</v>
+        <v>119044.72</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0890068198961</v>
+        <v>0.0917698585452</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1778,13 +1760,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="14">
-        <v>7750118</v>
+        <v>8074337</v>
       </c>
       <c r="G11" s="15">
-        <v>97093.48</v>
+        <v>116738.76</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0835814270446</v>
+        <v>0.0899922272231</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1807,13 +1789,13 @@
         <v>23</v>
       </c>
       <c r="F12" s="14">
-        <v>2291947</v>
+        <v>2466709</v>
       </c>
       <c r="G12" s="15">
-        <v>81762.92</v>
+        <v>90654.02</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0703843505551</v>
+        <v>0.0698838771846</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1836,13 +1818,13 @@
         <v>26</v>
       </c>
       <c r="F13" s="14">
-        <v>5120575</v>
+        <v>6124700</v>
       </c>
       <c r="G13" s="15">
-        <v>64780.39</v>
+        <v>87025.86</v>
       </c>
       <c r="H13" s="16">
-        <v>0.055765201131</v>
+        <v>0.0670869809428</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1865,13 +1847,13 @@
         <v>29</v>
       </c>
       <c r="F14" s="14">
-        <v>471173</v>
+        <v>422202</v>
       </c>
       <c r="G14" s="15">
-        <v>58004.46</v>
+        <v>52011.06</v>
       </c>
       <c r="H14" s="16">
-        <v>0.049932246138</v>
+        <v>0.0400945763826</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1891,16 +1873,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F15" s="14">
-        <v>457457</v>
+        <v>4212253</v>
       </c>
       <c r="G15" s="15">
-        <v>52550.14</v>
+        <v>50218.48</v>
       </c>
       <c r="H15" s="16">
-        <v>0.045236978761</v>
+        <v>0.0387127023017</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1911,25 +1893,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="F16" s="14">
-        <v>2676523</v>
+        <v>445234</v>
       </c>
       <c r="G16" s="15">
-        <v>43528.29</v>
+        <v>49910.73</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0374706581226</v>
+        <v>0.0384754622631</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1940,25 +1922,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="F17" s="14">
-        <v>3657001</v>
+        <v>2358753</v>
       </c>
       <c r="G17" s="15">
-        <v>36061.69</v>
+        <v>43783.17</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0310431504962</v>
+        <v>0.0337518145917</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1981,13 +1963,13 @@
         <v>40</v>
       </c>
       <c r="F18" s="14">
-        <v>1169467</v>
+        <v>1288802</v>
       </c>
       <c r="G18" s="15">
-        <v>34078.85</v>
+        <v>42119.34</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0293362532174</v>
+        <v>0.0324691920298</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2010,13 +1992,13 @@
         <v>29</v>
       </c>
       <c r="F19" s="14">
-        <v>681385</v>
+        <v>791949</v>
       </c>
       <c r="G19" s="15">
-        <v>29566.32</v>
+        <v>34127.46</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0254517112586</v>
+        <v>0.0263083669457</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2039,13 +2021,13 @@
         <v>45</v>
       </c>
       <c r="F20" s="14">
-        <v>7860450</v>
+        <v>9237466</v>
       </c>
       <c r="G20" s="15">
-        <v>25467.86</v>
+        <v>30843.90</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0219236150828</v>
+        <v>0.0237771178762</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2068,13 +2050,13 @@
         <v>48</v>
       </c>
       <c r="F21" s="14">
-        <v>1449251</v>
+        <v>3680437</v>
       </c>
       <c r="G21" s="15">
-        <v>25274.21</v>
+        <v>29364.37</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0217569144625</v>
+        <v>0.0226365695275</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2097,13 +2079,13 @@
         <v>51</v>
       </c>
       <c r="F22" s="14">
-        <v>550823</v>
+        <v>1597878</v>
       </c>
       <c r="G22" s="15">
-        <v>23819.51</v>
+        <v>26806</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0205046583694</v>
+        <v>0.020664358975</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2126,13 +2108,13 @@
         <v>54</v>
       </c>
       <c r="F23" s="14">
-        <v>2888196</v>
+        <v>2888351</v>
       </c>
       <c r="G23" s="15">
-        <v>18428.13</v>
+        <v>22438.15</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0158635719222</v>
+        <v>0.0172972463752</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2152,16 +2134,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F24" s="14">
-        <v>2779890</v>
+        <v>2929745</v>
       </c>
       <c r="G24" s="15">
-        <v>17124.12</v>
+        <v>21079.52</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0147410349951</v>
+        <v>0.0162498980937</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2184,13 +2166,13 @@
         <v>59</v>
       </c>
       <c r="F25" s="14">
-        <v>2176824</v>
+        <v>351537</v>
       </c>
       <c r="G25" s="15">
-        <v>16218.43</v>
+        <v>18736.92</v>
       </c>
       <c r="H25" s="16">
-        <v>0.013961385706</v>
+        <v>0.0144440215237</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2210,16 +2192,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F26" s="14">
-        <v>821899</v>
+        <v>4287826</v>
       </c>
       <c r="G26" s="15">
-        <v>15626.77</v>
+        <v>18675.63</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0134520643064</v>
+        <v>0.0143967739463</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2230,25 +2212,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F27" s="14">
-        <v>738004</v>
+        <v>2779890</v>
       </c>
       <c r="G27" s="15">
-        <v>15353.80</v>
+        <v>18413.99</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0132170822856</v>
+        <v>0.014195079442</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2259,25 +2241,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F28" s="14">
-        <v>53424</v>
+        <v>812006</v>
       </c>
       <c r="G28" s="15">
-        <v>14849.68</v>
+        <v>14715.17</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0127831183469</v>
+        <v>0.0113437124247</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2288,25 +2270,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F29" s="14">
-        <v>1892095</v>
+        <v>969376</v>
       </c>
       <c r="G29" s="15">
-        <v>13549.29</v>
+        <v>14216.87</v>
       </c>
       <c r="H29" s="16">
-        <v>0.011663697641</v>
+        <v>0.010959580138</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2317,25 +2299,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F30" s="14">
-        <v>812006</v>
+        <v>290710</v>
       </c>
       <c r="G30" s="15">
-        <v>12046.92</v>
+        <v>13904.66</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0103704055626</v>
+        <v>0.0107189019497</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2346,25 +2328,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>614847</v>
+        <v>461490</v>
       </c>
       <c r="G31" s="15">
-        <v>11426.93</v>
+        <v>13737.63</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0098366967188</v>
+        <v>0.0105901409306</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2375,25 +2357,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F32" s="14">
-        <v>290710</v>
+        <v>895656</v>
       </c>
       <c r="G32" s="15">
-        <v>11250.19</v>
+        <v>13459.02</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0096845528116</v>
+        <v>0.0103753644979</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2404,25 +2386,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F33" s="14">
-        <v>184412</v>
+        <v>550239</v>
       </c>
       <c r="G33" s="15">
-        <v>11199.99</v>
+        <v>12430.45</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0096413389146</v>
+        <v>0.0095824547124</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2433,25 +2415,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F34" s="14">
-        <v>13447615</v>
+        <v>614847</v>
       </c>
       <c r="G34" s="15">
-        <v>10832.05</v>
+        <v>11530.84</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0093246034318</v>
+        <v>0.0088889583318</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2462,25 +2444,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F35" s="14">
-        <v>2450000</v>
+        <v>1620490</v>
       </c>
       <c r="G35" s="15">
-        <v>10814.30</v>
+        <v>10265.8</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0093093236177</v>
+        <v>0.0079137572321</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2491,25 +2473,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F36" s="14">
-        <v>895656</v>
+        <v>11474864</v>
       </c>
       <c r="G36" s="15">
-        <v>9993.28</v>
+        <v>10030.18</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0086025611941</v>
+        <v>0.0077321211707</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2520,25 +2502,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F37" s="14">
-        <v>1620490</v>
+        <v>3885497</v>
       </c>
       <c r="G37" s="15">
-        <v>9630.57</v>
+        <v>9696.26</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0082903278763</v>
+        <v>0.0074747070564</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2558,16 +2540,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F38" s="14">
-        <v>803018</v>
+        <v>31842</v>
       </c>
       <c r="G38" s="15">
-        <v>9410.57</v>
+        <v>9423.64</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0081009442642</v>
+        <v>0.0072645482284</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2587,16 +2569,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="F39" s="14">
-        <v>3795497</v>
+        <v>19201</v>
       </c>
       <c r="G39" s="15">
-        <v>8099.21</v>
+        <v>8905.42</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0069720802028</v>
+        <v>0.0068650599009</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2607,25 +2589,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="F40" s="14">
-        <v>2569507</v>
+        <v>499193</v>
       </c>
       <c r="G40" s="15">
-        <v>7750.92</v>
+        <v>8663.99</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0066722601199</v>
+        <v>0.0066789449942</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2636,25 +2618,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F41" s="14">
-        <v>177268</v>
+        <v>257385</v>
       </c>
       <c r="G41" s="15">
-        <v>7354.32</v>
+        <v>8405.16</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0063308531174</v>
+        <v>0.0064794166784</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2665,25 +2647,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="F42" s="14">
-        <v>4822781</v>
+        <v>4009745</v>
       </c>
       <c r="G42" s="15">
-        <v>7319.05</v>
+        <v>8041.54</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0063004914811</v>
+        <v>0.0061991072622</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2694,25 +2676,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="F43" s="14">
-        <v>237785</v>
+        <v>3385220</v>
       </c>
       <c r="G43" s="15">
-        <v>7109.41</v>
+        <v>7990.13</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0061200261155</v>
+        <v>0.0061594760343</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2723,25 +2705,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F44" s="14">
-        <v>4009745</v>
+        <v>91000</v>
       </c>
       <c r="G44" s="15">
-        <v>7001.01</v>
+        <v>7832.37</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0060267116448</v>
+        <v>0.0060378611245</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2752,25 +2734,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="F45" s="14">
-        <v>303900</v>
+        <v>5160062</v>
       </c>
       <c r="G45" s="15">
-        <v>6992.13</v>
+        <v>7574.46</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0060190674335</v>
+        <v>0.0058390420235</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2781,25 +2763,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F46" s="14">
-        <v>402136</v>
+        <v>4822781</v>
       </c>
       <c r="G46" s="15">
-        <v>6064.01</v>
+        <v>7530.77</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0052201096243</v>
+        <v>0.0058053620323</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2810,25 +2792,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F47" s="14">
-        <v>5160062</v>
+        <v>2353507</v>
       </c>
       <c r="G47" s="15">
-        <v>5959.36</v>
+        <v>6819.29</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0051300232834</v>
+        <v>0.0052568923567</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2839,25 +2821,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F48" s="14">
-        <v>1057003</v>
+        <v>173145</v>
       </c>
       <c r="G48" s="15">
-        <v>5860.55</v>
+        <v>6785.21</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0050449642166</v>
+        <v>0.005230620576</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2868,25 +2850,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F49" s="14">
-        <v>12891</v>
+        <v>257325</v>
       </c>
       <c r="G49" s="15">
-        <v>5765.31</v>
+        <v>6376.90</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0049629783292</v>
+        <v>0.004915860283</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2906,16 +2888,16 @@
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F50" s="14">
-        <v>1099580</v>
+        <v>131237</v>
       </c>
       <c r="G50" s="15">
-        <v>4889.83</v>
+        <v>6162.89</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0042093348534</v>
+        <v>0.0047508830591</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2935,16 +2917,16 @@
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F51" s="14">
-        <v>380320</v>
+        <v>318644</v>
       </c>
       <c r="G51" s="15">
-        <v>4440.24</v>
+        <v>5885.99</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0038223122255</v>
+        <v>0.0045374248408</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2964,16 +2946,16 @@
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="F52" s="14">
-        <v>483909</v>
+        <v>1057003</v>
       </c>
       <c r="G52" s="15">
-        <v>4009.67</v>
+        <v>5659.72</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0034516626716</v>
+        <v>0.0043629965596</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2984,25 +2966,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F53" s="14">
-        <v>134078</v>
+        <v>380320</v>
       </c>
       <c r="G53" s="15">
-        <v>3831.68</v>
+        <v>5227.12</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0032984427211</v>
+        <v>0.0040295114558</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3013,25 +2995,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="F54" s="14">
-        <v>218223</v>
+        <v>1099580</v>
       </c>
       <c r="G54" s="15">
-        <v>3660.80</v>
+        <v>5159.78</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0031513433046</v>
+        <v>0.0039776000206</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3042,25 +3024,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F55" s="14">
-        <v>193145</v>
+        <v>433630</v>
       </c>
       <c r="G55" s="15">
-        <v>3604.76</v>
+        <v>4977.21</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0031031021336</v>
+        <v>0.0038368594394</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3071,25 +3053,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="F56" s="14">
-        <v>741553</v>
+        <v>76274</v>
       </c>
       <c r="G56" s="15">
-        <v>3529.05</v>
+        <v>4554.32</v>
       </c>
       <c r="H56" s="16">
-        <v>0.003037928346</v>
+        <v>0.0035108596346</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3100,25 +3082,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="F57" s="14">
-        <v>673669</v>
+        <v>1804173</v>
       </c>
       <c r="G57" s="15">
-        <v>3454.57</v>
+        <v>4319.19</v>
       </c>
       <c r="H57" s="16">
-        <v>0.002973813385</v>
+        <v>0.0033296013072</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3129,25 +3111,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="F58" s="14">
-        <v>99953</v>
+        <v>134078</v>
       </c>
       <c r="G58" s="15">
-        <v>3424.19</v>
+        <v>4189.4</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0029476612299</v>
+        <v>0.0032295480672</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3158,25 +3140,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F59" s="14">
-        <v>48057</v>
+        <v>741553</v>
       </c>
       <c r="G59" s="15">
-        <v>3020.72</v>
+        <v>4049.99</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0026003402937</v>
+        <v>0.0031220789079</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3187,25 +3169,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="F60" s="14">
-        <v>58578</v>
+        <v>88136</v>
       </c>
       <c r="G60" s="15">
-        <v>2965.83</v>
+        <v>3691.75</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0025530890825</v>
+        <v>0.0028459168561</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3216,25 +3198,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="F61" s="14">
-        <v>30299</v>
+        <v>651169</v>
       </c>
       <c r="G61" s="15">
-        <v>2836.79</v>
+        <v>3604.22</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0024420069857</v>
+        <v>0.0027784412409</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3245,25 +3227,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F62" s="14">
-        <v>808584</v>
+        <v>30299</v>
       </c>
       <c r="G62" s="15">
-        <v>2795.27</v>
+        <v>3594.82</v>
       </c>
       <c r="H62" s="16">
-        <v>0.002406265133</v>
+        <v>0.0027711949164</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3274,25 +3256,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="F63" s="14">
-        <v>77596</v>
+        <v>63463</v>
       </c>
       <c r="G63" s="15">
-        <v>2703.25</v>
+        <v>3488.88</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0023270511331</v>
+        <v>0.0026895272976</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3312,16 +3294,16 @@
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F64" s="14">
-        <v>70000</v>
+        <v>48057</v>
       </c>
       <c r="G64" s="15">
-        <v>2619.51</v>
+        <v>3429.59</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0022549648437</v>
+        <v>0.0026438214913</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3341,16 +3323,16 @@
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="F65" s="14">
-        <v>269892</v>
+        <v>72325</v>
       </c>
       <c r="G65" s="15">
-        <v>2618.63</v>
+        <v>3081.91</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0022542073093</v>
+        <v>0.0023757999913</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3370,16 +3352,16 @@
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="F66" s="14">
-        <v>183211</v>
+        <v>77596</v>
       </c>
       <c r="G66" s="15">
-        <v>2490.75</v>
+        <v>2967.04</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0021441237806</v>
+        <v>0.0022872483642</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3390,25 +3372,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F67" s="14">
-        <v>51463</v>
+        <v>113678</v>
       </c>
       <c r="G67" s="15">
-        <v>2488.16</v>
+        <v>2810.35</v>
       </c>
       <c r="H67" s="16">
-        <v>0.002141894219</v>
+        <v>0.002166458302</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3419,25 +3401,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F68" s="14">
-        <v>65400</v>
+        <v>808584</v>
       </c>
       <c r="G68" s="15">
-        <v>2396.68</v>
+        <v>2658.62</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0020631450697</v>
+        <v>0.0020494918323</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3448,25 +3430,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="F69" s="14">
-        <v>101702</v>
+        <v>1197222</v>
       </c>
       <c r="G69" s="15">
-        <v>2101.57</v>
+        <v>2469.87</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0018091041708</v>
+        <v>0.0019039871783</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3477,25 +3459,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="F70" s="14">
-        <v>126475</v>
+        <v>368157</v>
       </c>
       <c r="G70" s="15">
-        <v>2076.47</v>
+        <v>2380.32</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0017874972224</v>
+        <v>0.0018349543742</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3506,25 +3488,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="F71" s="14">
-        <v>923104</v>
+        <v>101702</v>
       </c>
       <c r="G71" s="15">
-        <v>2013.11</v>
+        <v>2372.2</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0017329547421</v>
+        <v>0.0018286947832</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3535,25 +3517,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="F72" s="14">
-        <v>249048</v>
+        <v>90800</v>
       </c>
       <c r="G72" s="15">
-        <v>1859.52</v>
+        <v>1883.83</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0016007391558</v>
+        <v>0.0014522173904</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3564,25 +3546,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="F73" s="14">
-        <v>683762</v>
+        <v>923104</v>
       </c>
       <c r="G73" s="15">
-        <v>1482.60</v>
+        <v>1823.04</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0012762733783</v>
+        <v>0.0014053552557</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3593,25 +3575,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F74" s="14">
-        <v>224363</v>
+        <v>50234</v>
       </c>
       <c r="G74" s="15">
-        <v>1309.83</v>
+        <v>1594.78</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0011275469844</v>
+        <v>0.0012293929122</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3622,10 +3604,10 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
@@ -3637,10 +3619,10 @@
         <v>119121</v>
       </c>
       <c r="G75" s="15">
-        <v>1007.11</v>
+        <v>1136.95</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0008669551342</v>
+        <v>0.0008764583651</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3651,25 +3633,25 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="F76" s="14">
-        <v>24569</v>
+        <v>127144</v>
       </c>
       <c r="G76" s="15">
-        <v>967.23</v>
+        <v>1127.96</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0008326250504</v>
+        <v>0.0008695281037</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3692,13 +3674,13 @@
         <v>181</v>
       </c>
       <c r="F77" s="14">
-        <v>3121</v>
+        <v>3654</v>
       </c>
       <c r="G77" s="15">
-        <v>932.94</v>
+        <v>1069.71</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0008031070319</v>
+        <v>0.0008246240184</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3718,16 +3700,16 @@
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F78" s="14">
-        <v>34253</v>
+        <v>673266</v>
       </c>
       <c r="G78" s="15">
-        <v>859.36</v>
+        <v>1030.9</v>
       </c>
       <c r="H78" s="16">
-        <v>0.000739766822</v>
+        <v>0.0007947059489</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3747,16 +3729,16 @@
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="F79" s="14">
-        <v>710690</v>
+        <v>51475</v>
       </c>
       <c r="G79" s="15">
-        <v>782.26</v>
+        <v>791.22</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0006733964744</v>
+        <v>0.000609940092</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3776,16 +3758,16 @@
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="F80" s="14">
-        <v>90450</v>
+        <v>147789</v>
       </c>
       <c r="G80" s="15">
-        <v>237.53</v>
+        <v>630.76</v>
       </c>
       <c r="H80" s="16">
-        <v>0.0002044740426</v>
+        <v>0.0004862437912</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -3796,25 +3778,25 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C81" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C81" s="13" t="s">
-        <v>190</v>
-      </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="F81" s="14">
-        <v>78527</v>
+        <v>113505</v>
       </c>
       <c r="G81" s="15">
-        <v>162.41</v>
+        <v>378.03</v>
       </c>
       <c r="H81" s="16">
-        <v>0.0001398081474</v>
+        <v>0.0002914178774</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -3825,25 +3807,25 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C82" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>192</v>
-      </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F82" s="14">
-        <v>50580</v>
+        <v>78527</v>
       </c>
       <c r="G82" s="15">
-        <v>107.99</v>
+        <v>188.55</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0000929615284</v>
+        <v>0.0001453504769</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -3854,64 +3836,64 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9">
+        <v>35965.72</v>
+      </c>
+      <c r="H84" s="10">
+        <v>0.02772545508</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C85" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D83" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F83" s="14">
-        <v>24734</v>
-      </c>
-      <c r="G83" s="15">
-        <v>64.58</v>
-      </c>
-      <c r="H83" s="16">
-        <v>0.0000555926984</v>
-      </c>
-      <c r="I83" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
+      <c r="D85" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9">
-        <v>35985.11</v>
-      </c>
-      <c r="H85" s="10">
-        <v>0.0309772277825</v>
-      </c>
-      <c r="I85" s="9" t="s">
+      <c r="F85" s="14">
+        <v>1596210</v>
+      </c>
+      <c r="G85" s="15">
+        <v>35965.72</v>
+      </c>
+      <c r="H85" s="16">
+        <v>0.02772545508</v>
+      </c>
+      <c r="I85" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J85" s="11" t="s">
@@ -3920,435 +3902,435 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D86" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="13" t="s">
+      <c r="H87" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F86" s="14">
-        <v>1596210</v>
-      </c>
-      <c r="G86" s="15">
-        <v>35985.11</v>
-      </c>
-      <c r="H86" s="16">
-        <v>0.0309772277825</v>
-      </c>
-      <c r="I86" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="7" t="s">
+      <c r="C89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1">
+      <c r="B91" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1">
+      <c r="B92" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1">
+      <c r="B93" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="9" t="s">
+      <c r="C93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" ht="15" customHeight="1">
+      <c r="B94" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" ht="15" customHeight="1">
+      <c r="B95" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="H88" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="7" t="s">
+      <c r="C95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" ht="15" customHeight="1">
+      <c r="B96" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" ht="15" customHeight="1">
+      <c r="B97" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H90" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H92" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="7" t="s">
+      <c r="C97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15" customHeight="1">
+      <c r="B98" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" ht="15" customHeight="1">
+      <c r="B99" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J95" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="7" t="s">
+      <c r="C99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15" customHeight="1">
+      <c r="B100" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="15" customHeight="1">
+      <c r="B101" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J96" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J97" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="7" t="s">
+      <c r="C101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9">
+        <v>15411.87</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.0118807884112</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="15" customHeight="1">
+      <c r="B102" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15" customHeight="1">
+      <c r="B103" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J98" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="7" t="s">
+      <c r="C103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" ht="15" customHeight="1">
+      <c r="B104" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" ht="15" customHeight="1">
+      <c r="B105" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="7" t="s">
+      <c r="C105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" ht="15" customHeight="1">
+      <c r="B106" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" ht="15" customHeight="1">
+      <c r="B107" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="9">
-        <v>22411.33</v>
-      </c>
-      <c r="H102" s="10">
-        <v>0.0192924483018</v>
-      </c>
-      <c r="I102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="7" t="s">
+      <c r="C107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="9">
+        <v>15411.87</v>
+      </c>
+      <c r="H107" s="10">
+        <v>0.0118807884112</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" ht="15" customHeight="1">
+      <c r="B108" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H104" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J105" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="7" t="s">
+      <c r="C108" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="I106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J106" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="7" t="s">
+      <c r="D108" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="9">
-        <v>22411.33</v>
-      </c>
-      <c r="H108" s="10">
-        <v>0.0192924483018</v>
-      </c>
-      <c r="I108" s="9" t="s">
-        <v>13</v>
+      <c r="F108" s="14">
+        <v>5000000</v>
+      </c>
+      <c r="G108" s="15">
+        <v>4991.43</v>
+      </c>
+      <c r="H108" s="16">
+        <v>0.0038478214324</v>
+      </c>
+      <c r="I108" s="15">
+        <v>5.70</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4365,19 +4347,19 @@
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F109" s="14">
-        <v>6300000</v>
+        <v>5000000</v>
       </c>
       <c r="G109" s="15">
-        <v>6294.51</v>
+        <v>4975.47</v>
       </c>
       <c r="H109" s="16">
-        <v>0.0054185319997</v>
+        <v>0.0038355180985</v>
       </c>
       <c r="I109" s="15">
-        <v>6.37</v>
+        <v>5.62</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
@@ -4385,28 +4367,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F110" s="14">
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="G110" s="15">
-        <v>5229.96</v>
+        <v>4949.01</v>
       </c>
       <c r="H110" s="16">
-        <v>0.004502130526</v>
+        <v>0.0038151204659</v>
       </c>
       <c r="I110" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>13</v>
@@ -4414,28 +4396,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C111" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C111" s="13" t="s">
-        <v>215</v>
-      </c>
       <c r="D111" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F111" s="14">
-        <v>5100000</v>
+        <v>500000</v>
       </c>
       <c r="G111" s="15">
-        <v>5051.1</v>
+        <v>495.96</v>
       </c>
       <c r="H111" s="16">
-        <v>0.0043481616494</v>
+        <v>0.0003823284144</v>
       </c>
       <c r="I111" s="15">
-        <v>6.43</v>
+        <v>5.61</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
@@ -4443,57 +4425,36 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
       <c r="B112" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C112" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F112" s="14">
-        <v>2500000</v>
-      </c>
-      <c r="G112" s="15">
-        <v>2463.95</v>
-      </c>
-      <c r="H112" s="16">
-        <v>0.0021210534133</v>
-      </c>
-      <c r="I112" s="15">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C113" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F113" s="14">
-        <v>2000000</v>
-      </c>
-      <c r="G113" s="15">
-        <v>1975.99</v>
-      </c>
-      <c r="H113" s="16">
-        <v>0.0017010005617</v>
-      </c>
-      <c r="I113" s="15">
-        <v>6.52</v>
+      <c r="B113" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
@@ -4501,57 +4462,36 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F114" s="14">
-        <v>1300000</v>
-      </c>
-      <c r="G114" s="15">
-        <v>1297.26</v>
-      </c>
-      <c r="H114" s="16">
-        <v>0.0011167262935</v>
-      </c>
-      <c r="I114" s="15">
-        <v>6.42</v>
+        <v>13</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C115" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F115" s="14">
-        <v>100000</v>
-      </c>
-      <c r="G115" s="15">
-        <v>98.56</v>
-      </c>
-      <c r="H115" s="16">
-        <v>0.0000848438582</v>
-      </c>
-      <c r="I115" s="15">
-        <v>6.51</v>
+      <c r="B115" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I115" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
@@ -4567,7 +4507,7 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="7" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>13</v>
@@ -4581,11 +4521,11 @@
       <c r="F117" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G117" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>200</v>
+      <c r="G117" s="9">
+        <v>57361.84</v>
+      </c>
+      <c r="H117" s="10">
+        <v>0.0442194155498</v>
       </c>
       <c r="I117" s="9" t="s">
         <v>13</v>
@@ -4604,7 +4544,7 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>13</v>
@@ -4618,11 +4558,11 @@
       <c r="F119" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G119" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>200</v>
+      <c r="G119" s="9">
+        <v>2320</v>
+      </c>
+      <c r="H119" s="10">
+        <v>0.0017884545557</v>
       </c>
       <c r="I119" s="9" t="s">
         <v>13</v>
@@ -4633,6 +4573,20 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="13"/>
+      <c r="G120" s="15">
+        <v>2320</v>
+      </c>
+      <c r="H120" s="16">
+        <v>0.0017884545557</v>
+      </c>
+      <c r="I120" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J120" s="11" t="s">
@@ -4640,247 +4594,267 @@
       </c>
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" ht="15" customHeight="1">
+      <c r="B122" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C122" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="18">
+        <v>-2568.81423363043</v>
+      </c>
+      <c r="H122" s="19">
+        <v>-0.001980261861671664</v>
+      </c>
+      <c r="I122" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J122" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" ht="15" customHeight="1">
+      <c r="B123" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="18">
+        <v>1297209.36576637</v>
+      </c>
+      <c r="H123" s="19">
+        <v>0.9999999999955281</v>
+      </c>
+      <c r="I123" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" ht="15" customHeight="1">
+      <c r="B125" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C125" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H125" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8" ht="15" customHeight="1">
+      <c r="B126" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E126" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F126" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G126" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H126" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8" ht="15" customHeight="1">
+      <c r="B127" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" ht="15" customHeight="1">
+      <c r="B128" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G121" s="9">
-        <v>66177.53</v>
-      </c>
-      <c r="H121" s="10">
-        <v>0.0569679075844</v>
-      </c>
-      <c r="I121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J121" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122" spans="2:10" ht="15" customHeight="1">
-      <c r="B122" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J122" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="7" t="s">
+      <c r="C128" s="13"/>
+      <c r="D128" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="9">
-        <v>2655</v>
-      </c>
-      <c r="H123" s="10">
-        <v>0.0022855158637</v>
-      </c>
-      <c r="I123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="12" t="s">
+      <c r="F128" s="14">
+        <v>177150</v>
+      </c>
+      <c r="G128" s="15">
+        <v>44059.33</v>
+      </c>
+      <c r="H128" s="16">
+        <v>0.0339647023547</v>
+      </c>
+      <c r="I128" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" ht="15" customHeight="1">
+      <c r="B129" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="13"/>
-      <c r="G124" s="15">
-        <v>2655</v>
-      </c>
-      <c r="H124" s="16">
-        <v>0.0022855158637</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" ht="15" customHeight="1">
-      <c r="B125" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J125" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="17" t="s">
+      <c r="C129" s="13"/>
+      <c r="D129" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F129" s="14">
+        <v>-46250</v>
+      </c>
+      <c r="G129" s="15">
+        <v>-555.05</v>
+      </c>
+      <c r="H129" s="16">
+        <v>-0.0004278800436</v>
+      </c>
+      <c r="I129" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15" customHeight="1">
+      <c r="B130" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C126" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F126" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="18">
-        <v>-1724.8964428005274</v>
-      </c>
-      <c r="H126" s="19">
-        <v>-0.0014848505398462667</v>
-      </c>
-      <c r="I126" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="17" t="s">
+      <c r="C130" s="13"/>
+      <c r="D130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F130" s="14">
+        <v>-90800</v>
+      </c>
+      <c r="G130" s="15">
+        <v>-1896.18</v>
+      </c>
+      <c r="H130" s="16">
+        <v>-0.0014617378274</v>
+      </c>
+      <c r="I130" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" ht="15" customHeight="1">
+      <c r="B131" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C127" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D127" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="18">
-        <v>1161663.3435572</v>
-      </c>
-      <c r="H127" s="19">
-        <v>0.9999999999957542</v>
-      </c>
-      <c r="I127" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J127" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8" ht="15" customHeight="1">
-      <c r="B129" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="C129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H129" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="2:8" ht="15" customHeight="1">
-      <c r="B130" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C130" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E130" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F130" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G130" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H130" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="2:8" ht="15" customHeight="1">
-      <c r="B131" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H131" s="8" t="s">
+      <c r="C131" s="13"/>
+      <c r="D131" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F131" s="14">
+        <v>-1272425</v>
+      </c>
+      <c r="G131" s="15">
+        <v>-3064.25</v>
+      </c>
+      <c r="H131" s="16">
+        <v>-0.0023621861519</v>
+      </c>
+      <c r="I131" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
       <c r="B132" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C132" s="13"/>
       <c r="D132" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="F132" s="14">
-        <v>164100</v>
+        <v>-1073800</v>
       </c>
       <c r="G132" s="15">
-        <v>38760.75</v>
+        <v>-15627.01</v>
       </c>
       <c r="H132" s="16">
-        <v>0.0333665947324</v>
+        <v>-0.012046636736</v>
       </c>
       <c r="I132" s="15" t="s">
         <v>13</v>
@@ -4891,23 +4865,23 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
       <c r="B133" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C133" s="13"/>
       <c r="D133" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F133" s="14">
-        <v>-22500</v>
+        <v>-2374900</v>
       </c>
       <c r="G133" s="15">
-        <v>-116.08</v>
+        <v>-17020.91</v>
       </c>
       <c r="H133" s="16">
-        <v>-0.0000999256803</v>
+        <v>-0.0131211741521</v>
       </c>
       <c r="I133" s="15" t="s">
         <v>13</v>
@@ -4918,7 +4892,7 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
       <c r="B134" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C134" s="13"/>
       <c r="D134" s="13" t="s">
@@ -4928,13 +4902,13 @@
         <v>26</v>
       </c>
       <c r="F134" s="14">
-        <v>-1028000</v>
+        <v>-1500000</v>
       </c>
       <c r="G134" s="15">
-        <v>-13056.11</v>
+        <v>-21442.50</v>
       </c>
       <c r="H134" s="16">
-        <v>-0.0112391512329</v>
+        <v>-0.0165297141432</v>
       </c>
       <c r="I134" s="15" t="s">
         <v>13</v>
@@ -4943,102 +4917,44 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="2:10" ht="15" customHeight="1">
-      <c r="B135" s="12" t="s">
+    <row r="138" spans="2:9" ht="15" customHeight="1">
+      <c r="B138" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C138" s="21"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="21"/>
+    </row>
+    <row r="142" spans="2:9" ht="15" customHeight="1">
+      <c r="B142" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
+      <c r="I142" s="21"/>
+    </row>
+    <row r="143" spans="2:8" ht="15" customHeight="1">
+      <c r="B143" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C143" s="21"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
+    </row>
+    <row r="145" spans="2:8" ht="15" customHeight="1">
+      <c r="B145" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="C135" s="13"/>
-      <c r="D135" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F135" s="14">
-        <v>-725900</v>
-      </c>
-      <c r="G135" s="15">
-        <v>-15161.15</v>
-      </c>
-      <c r="H135" s="16">
-        <v>-0.0130512424998</v>
-      </c>
-      <c r="I135" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J135" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" ht="15" customHeight="1">
-      <c r="B136" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C136" s="13"/>
-      <c r="D136" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F136" s="14">
-        <v>-821600</v>
-      </c>
-      <c r="G136" s="15">
-        <v>-15702.01</v>
-      </c>
-      <c r="H136" s="16">
-        <v>-0.0135168335017</v>
-      </c>
-      <c r="I136" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J136" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" ht="15" customHeight="1">
-      <c r="B137" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C137" s="13"/>
-      <c r="D137" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F137" s="14">
-        <v>-1948800</v>
-      </c>
-      <c r="G137" s="15">
-        <v>-24505.190000000002</v>
-      </c>
-      <c r="H137" s="16">
-        <v>-0.0210949154382</v>
-      </c>
-      <c r="I137" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J137" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9" ht="15" customHeight="1">
-      <c r="B141" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C141" s="21"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="21"/>
-      <c r="F141" s="21"/>
-      <c r="G141" s="21"/>
-      <c r="H141" s="21"/>
-      <c r="I141" s="21"/>
-    </row>
-    <row r="145" spans="2:9" ht="15" customHeight="1">
-      <c r="B145" s="13" t="s">
-        <v>238</v>
       </c>
       <c r="C145" s="21"/>
       <c r="D145" s="21"/>
@@ -5046,34 +4962,38 @@
       <c r="F145" s="21"/>
       <c r="G145" s="21"/>
       <c r="H145" s="21"/>
-      <c r="I145" s="21"/>
-    </row>
-    <row r="146" spans="2:8" ht="15" customHeight="1">
-      <c r="B146" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="C146" s="21"/>
-      <c r="D146" s="21"/>
-      <c r="E146" s="21"/>
-      <c r="F146" s="21"/>
-      <c r="G146" s="21"/>
-      <c r="H146" s="21"/>
-    </row>
-    <row r="148" spans="2:8" ht="15" customHeight="1">
-      <c r="B148" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C148" s="21"/>
-      <c r="D148" s="21"/>
-      <c r="E148" s="21"/>
-      <c r="F148" s="21"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21"/>
+    </row>
+    <row r="147" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B147" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="C147" s="23"/>
+      <c r="D147" s="23"/>
+      <c r="E147" s="23"/>
+      <c r="F147" s="23"/>
+      <c r="G147" s="23"/>
+      <c r="H147" s="23"/>
+    </row>
+    <row r="148" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B148" s="23"/>
+      <c r="C148" s="23"/>
+      <c r="D148" s="23"/>
+      <c r="E148" s="23"/>
+      <c r="F148" s="23"/>
+      <c r="G148" s="23"/>
+      <c r="H148" s="23"/>
+    </row>
+    <row r="149" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B149" s="23"/>
+      <c r="C149" s="23"/>
+      <c r="D149" s="23"/>
+      <c r="E149" s="23"/>
+      <c r="F149" s="23"/>
+      <c r="G149" s="23"/>
+      <c r="H149" s="23"/>
     </row>
     <row r="150" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B150" s="22" t="s">
-        <v>241</v>
-      </c>
+      <c r="B150" s="23"/>
       <c r="C150" s="23"/>
       <c r="D150" s="23"/>
       <c r="E150" s="23"/>
@@ -5099,36 +5019,42 @@
       <c r="G152" s="23"/>
       <c r="H152" s="23"/>
     </row>
-    <row r="153" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B153" s="23"/>
-      <c r="C153" s="23"/>
-      <c r="D153" s="23"/>
-      <c r="E153" s="23"/>
-      <c r="F153" s="23"/>
-      <c r="G153" s="23"/>
-      <c r="H153" s="23"/>
-    </row>
-    <row r="154" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B154" s="23"/>
-      <c r="C154" s="23"/>
-      <c r="D154" s="23"/>
-      <c r="E154" s="23"/>
-      <c r="F154" s="23"/>
-      <c r="G154" s="23"/>
-      <c r="H154" s="23"/>
-    </row>
-    <row r="155" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B155" s="23"/>
-      <c r="C155" s="23"/>
-      <c r="D155" s="23"/>
-      <c r="E155" s="23"/>
-      <c r="F155" s="23"/>
-      <c r="G155" s="23"/>
-      <c r="H155" s="23"/>
-    </row>
-    <row r="157" spans="2:8" ht="15" customHeight="1">
-      <c r="B157" s="13" t="s">
-        <v>242</v>
+    <row r="154" spans="2:8" ht="15" customHeight="1">
+      <c r="B154" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C154" s="21"/>
+      <c r="D154" s="21"/>
+      <c r="E154" s="21"/>
+      <c r="F154" s="21"/>
+      <c r="G154" s="21"/>
+      <c r="H154" s="21"/>
+    </row>
+    <row r="155" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B155" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="C155" s="21"/>
+      <c r="D155" s="21"/>
+      <c r="E155" s="21"/>
+      <c r="F155" s="21"/>
+      <c r="G155" s="21"/>
+      <c r="H155" s="21"/>
+    </row>
+    <row r="156" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B156" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C156" s="21"/>
+      <c r="D156" s="21"/>
+      <c r="E156" s="21"/>
+      <c r="F156" s="21"/>
+      <c r="G156" s="21"/>
+      <c r="H156" s="21"/>
+    </row>
+    <row r="157" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B157" s="24" t="s">
+        <v>239</v>
       </c>
       <c r="C157" s="21"/>
       <c r="D157" s="21"/>
@@ -5137,68 +5063,35 @@
       <c r="G157" s="21"/>
       <c r="H157" s="21"/>
     </row>
-    <row r="158" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B158" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="C158" s="21"/>
-      <c r="D158" s="21"/>
-      <c r="E158" s="21"/>
-      <c r="F158" s="21"/>
-      <c r="G158" s="21"/>
-      <c r="H158" s="21"/>
-    </row>
-    <row r="159" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B159" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="C159" s="21"/>
-      <c r="D159" s="21"/>
-      <c r="E159" s="21"/>
-      <c r="F159" s="21"/>
-      <c r="G159" s="21"/>
-      <c r="H159" s="21"/>
-    </row>
-    <row r="160" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B160" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="C160" s="21"/>
-      <c r="D160" s="21"/>
-      <c r="E160" s="21"/>
-      <c r="F160" s="21"/>
-      <c r="G160" s="21"/>
-      <c r="H160" s="21"/>
-    </row>
-    <row r="163" ht="15">
-      <c r="B163" s="21" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="178" ht="15">
-      <c r="B178" s="21" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="179" ht="15">
-      <c r="B179" s="21" t="s">
-        <v>248</v>
+    <row r="160" ht="15">
+      <c r="B160" s="21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="175" ht="15">
+      <c r="B175" s="21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="176" ht="15">
+      <c r="B176" s="21" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B159:H159"/>
-    <mergeCell ref="B160:H160"/>
-    <mergeCell ref="B146:H146"/>
-    <mergeCell ref="B148:H148"/>
-    <mergeCell ref="B150:H155"/>
+    <mergeCell ref="B156:H156"/>
     <mergeCell ref="B157:H157"/>
-    <mergeCell ref="B158:H158"/>
+    <mergeCell ref="B143:H143"/>
+    <mergeCell ref="B145:H145"/>
+    <mergeCell ref="B147:H152"/>
+    <mergeCell ref="B154:H154"/>
+    <mergeCell ref="B155:H155"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B141:I141"/>
-    <mergeCell ref="B145:I145"/>
+    <mergeCell ref="B138:I138"/>
+    <mergeCell ref="B142:I142"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
